--- a/Results_experiment/exp_4/preds_3364444555550000.xlsx
+++ b/Results_experiment/exp_4/preds_3364444555550000.xlsx
@@ -1443,7 +1443,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D2">
-        <v>1.587518930435181</v>
+        <v>1.356244087219238</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1457,7 +1457,7 @@
         <v>12.30000019073486</v>
       </c>
       <c r="D3">
-        <v>10.52766132354736</v>
+        <v>10.89558792114258</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1471,7 +1471,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D4">
-        <v>1.801401138305664</v>
+        <v>1.647028684616089</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1485,7 +1485,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D5">
-        <v>1.708492040634155</v>
+        <v>1.68498694896698</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1499,7 +1499,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D6">
-        <v>2.862583160400391</v>
+        <v>3.088440895080566</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1513,7 +1513,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D7">
-        <v>2.967894554138184</v>
+        <v>3.151779174804688</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1527,7 +1527,7 @@
         <v>18</v>
       </c>
       <c r="D8">
-        <v>1.969313383102417</v>
+        <v>4.355484485626221</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1541,7 +1541,7 @@
         <v>33.70000076293945</v>
       </c>
       <c r="D9">
-        <v>20.24677467346191</v>
+        <v>23.65699768066406</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1555,7 +1555,7 @@
         <v>24.39999961853027</v>
       </c>
       <c r="D10">
-        <v>11.47029209136963</v>
+        <v>15.10360622406006</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1569,7 +1569,7 @@
         <v>12</v>
       </c>
       <c r="D11">
-        <v>8.088640213012695</v>
+        <v>6.877349853515625</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1583,7 +1583,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D12">
-        <v>8.054173469543457</v>
+        <v>6.862580299377441</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1597,7 +1597,7 @@
         <v>19.60000038146973</v>
       </c>
       <c r="D13">
-        <v>17.07672309875488</v>
+        <v>18.80945205688477</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1611,7 +1611,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D14">
-        <v>1.656099796295166</v>
+        <v>1.349714040756226</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1625,7 +1625,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D15">
-        <v>1.240537524223328</v>
+        <v>1.277402639389038</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1639,7 +1639,7 @@
         <v>20.60000038146973</v>
       </c>
       <c r="D16">
-        <v>4.43507194519043</v>
+        <v>8.54030704498291</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1653,7 +1653,7 @@
         <v>9.5</v>
       </c>
       <c r="D17">
-        <v>5.155286312103271</v>
+        <v>5.838065624237061</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1667,7 +1667,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D18">
-        <v>13.45555782318115</v>
+        <v>16.84350967407227</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1681,7 +1681,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D19">
-        <v>1.217963099479675</v>
+        <v>1.23909854888916</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1695,7 +1695,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D20">
-        <v>7.933648586273193</v>
+        <v>5.477079391479492</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1709,7 +1709,7 @@
         <v>14</v>
       </c>
       <c r="D21">
-        <v>10.78719234466553</v>
+        <v>10.79314041137695</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1723,7 +1723,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D22">
-        <v>1.482810497283936</v>
+        <v>1.512669205665588</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1737,7 +1737,7 @@
         <v>12.39999961853027</v>
       </c>
       <c r="D23">
-        <v>8.88939380645752</v>
+        <v>7.463635444641113</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1751,7 +1751,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D24">
-        <v>8.236797332763672</v>
+        <v>6.785601615905762</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1765,7 +1765,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D25">
-        <v>3.004734992980957</v>
+        <v>3.916882514953613</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1779,7 +1779,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D26">
-        <v>6.970729351043701</v>
+        <v>1.300025105476379</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1793,7 +1793,7 @@
         <v>3</v>
       </c>
       <c r="D27">
-        <v>7.577906131744385</v>
+        <v>7.039680957794189</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1807,7 +1807,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D28">
-        <v>3.050590515136719</v>
+        <v>3.437428951263428</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1821,7 +1821,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D29">
-        <v>4.404109477996826</v>
+        <v>2.423200130462646</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1835,7 +1835,7 @@
         <v>18.79999923706055</v>
       </c>
       <c r="D30">
-        <v>8.06867790222168</v>
+        <v>6.583800792694092</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1849,7 +1849,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D31">
-        <v>1.714319944381714</v>
+        <v>1.475232124328613</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1863,7 +1863,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D32">
-        <v>2.804413080215454</v>
+        <v>5.545722484588623</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1877,7 +1877,7 @@
         <v>23.10000038146973</v>
       </c>
       <c r="D33">
-        <v>19.1207447052002</v>
+        <v>20.66500091552734</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1891,7 +1891,7 @@
         <v>19.39999961853027</v>
       </c>
       <c r="D34">
-        <v>20.1020336151123</v>
+        <v>20.26338577270508</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1905,7 +1905,7 @@
         <v>9.5</v>
       </c>
       <c r="D35">
-        <v>1.732691049575806</v>
+        <v>2.369572162628174</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1919,7 +1919,7 @@
         <v>1.5</v>
       </c>
       <c r="D36">
-        <v>1.569725751876831</v>
+        <v>1.970481872558594</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1933,7 +1933,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D37">
-        <v>4.185326099395752</v>
+        <v>3.585718631744385</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1947,7 +1947,7 @@
         <v>5.5</v>
       </c>
       <c r="D38">
-        <v>2.764223098754883</v>
+        <v>3.307239055633545</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1961,7 +1961,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D39">
-        <v>5.043120861053467</v>
+        <v>7.261710643768311</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1975,7 +1975,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D40">
-        <v>5.617518901824951</v>
+        <v>4.570878982543945</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1989,7 +1989,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D41">
-        <v>2.247366905212402</v>
+        <v>2.763265371322632</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2003,7 +2003,7 @@
         <v>16.70000076293945</v>
       </c>
       <c r="D42">
-        <v>10.2536096572876</v>
+        <v>7.437105655670166</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2017,7 +2017,7 @@
         <v>3.5</v>
       </c>
       <c r="D43">
-        <v>2.753635406494141</v>
+        <v>3.124995231628418</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2031,7 +2031,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D44">
-        <v>8.142651557922363</v>
+        <v>7.22869348526001</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2045,7 +2045,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D45">
-        <v>9.713199615478516</v>
+        <v>8.698726654052734</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2059,7 +2059,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D46">
-        <v>1.903223633766174</v>
+        <v>3.214202404022217</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2073,7 +2073,7 @@
         <v>3.5</v>
       </c>
       <c r="D47">
-        <v>1.954943418502808</v>
+        <v>2.553864240646362</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2087,7 +2087,7 @@
         <v>12.19999980926514</v>
       </c>
       <c r="D48">
-        <v>3.717381477355957</v>
+        <v>6.611950397491455</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2101,7 +2101,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D49">
-        <v>3.388453483581543</v>
+        <v>3.202919006347656</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2115,7 +2115,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D50">
-        <v>2.016530990600586</v>
+        <v>2.133585929870605</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2129,7 +2129,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D51">
-        <v>3.677392959594727</v>
+        <v>5.463154315948486</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2143,7 +2143,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D52">
-        <v>2.880990028381348</v>
+        <v>2.782701015472412</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2157,7 +2157,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D53">
-        <v>2.079980373382568</v>
+        <v>2.229631185531616</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2171,7 +2171,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D54">
-        <v>9.731504440307617</v>
+        <v>10.00944328308105</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2185,7 +2185,7 @@
         <v>3.5</v>
       </c>
       <c r="D55">
-        <v>3.251695156097412</v>
+        <v>3.239189147949219</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2199,7 +2199,7 @@
         <v>20.20000076293945</v>
       </c>
       <c r="D56">
-        <v>17.92282485961914</v>
+        <v>16.5056095123291</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2213,7 +2213,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D57">
-        <v>1.652258396148682</v>
+        <v>1.414336323738098</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2227,7 +2227,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D58">
-        <v>8.271183013916016</v>
+        <v>7.429849624633789</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2241,7 +2241,7 @@
         <v>29.79999923706055</v>
       </c>
       <c r="D59">
-        <v>17.1269359588623</v>
+        <v>18.93410110473633</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2255,7 +2255,7 @@
         <v>13.19999980926514</v>
       </c>
       <c r="D60">
-        <v>4.479340076446533</v>
+        <v>6.5680251121521</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2269,7 +2269,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D61">
-        <v>8.269426345825195</v>
+        <v>7.950991153717041</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2283,7 +2283,7 @@
         <v>16.10000038146973</v>
       </c>
       <c r="D62">
-        <v>6.038485050201416</v>
+        <v>7.476738452911377</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2297,7 +2297,7 @@
         <v>1</v>
       </c>
       <c r="D63">
-        <v>1.467702150344849</v>
+        <v>1.840675115585327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2311,7 +2311,7 @@
         <v>17.39999961853027</v>
       </c>
       <c r="D64">
-        <v>9.226517677307129</v>
+        <v>9.774658203125</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2325,7 +2325,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D65">
-        <v>1.704022884368896</v>
+        <v>3.313923835754395</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2339,7 +2339,7 @@
         <v>14.80000019073486</v>
       </c>
       <c r="D66">
-        <v>8.967791557312012</v>
+        <v>9.56419849395752</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2353,7 +2353,7 @@
         <v>5</v>
       </c>
       <c r="D67">
-        <v>1.492026448249817</v>
+        <v>1.532461524009705</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2367,7 +2367,7 @@
         <v>19.79999923706055</v>
       </c>
       <c r="D68">
-        <v>17.88830757141113</v>
+        <v>20.83812141418457</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2381,7 +2381,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D69">
-        <v>1.639235496520996</v>
+        <v>1.435874938964844</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2395,7 +2395,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D70">
-        <v>2.672306537628174</v>
+        <v>2.69946813583374</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2409,7 +2409,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D71">
-        <v>2.60000467300415</v>
+        <v>8.236078262329102</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2423,7 +2423,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D72">
-        <v>6.751168727874756</v>
+        <v>7.868412494659424</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2437,7 +2437,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D73">
-        <v>3.012160539627075</v>
+        <v>3.343224048614502</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2451,7 +2451,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D74">
-        <v>9.892434120178223</v>
+        <v>11.35635185241699</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2465,7 +2465,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D75">
-        <v>3.120577812194824</v>
+        <v>4.266116142272949</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2479,7 +2479,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D76">
-        <v>2.565873146057129</v>
+        <v>2.688409805297852</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2493,7 +2493,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D77">
-        <v>1.553450226783752</v>
+        <v>1.834802508354187</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2507,7 +2507,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D78">
-        <v>7.468907356262207</v>
+        <v>6.191272258758545</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2521,7 +2521,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D79">
-        <v>1.228936553001404</v>
+        <v>1.22056519985199</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2535,7 +2535,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D80">
-        <v>9.455060005187988</v>
+        <v>8.962658882141113</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2549,7 +2549,7 @@
         <v>21.29999923706055</v>
       </c>
       <c r="D81">
-        <v>5.488509178161621</v>
+        <v>6.634884834289551</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2563,7 +2563,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D82">
-        <v>7.761378288269043</v>
+        <v>4.040493011474609</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2577,7 +2577,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D83">
-        <v>5.935325622558594</v>
+        <v>4.790440559387207</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2591,7 +2591,7 @@
         <v>20.39999961853027</v>
       </c>
       <c r="D84">
-        <v>18.69799995422363</v>
+        <v>17.4769115447998</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2605,7 +2605,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D85">
-        <v>1.234340786933899</v>
+        <v>1.223049402236938</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2619,7 +2619,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D86">
-        <v>5.370385646820068</v>
+        <v>4.717015743255615</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2633,7 +2633,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D87">
-        <v>2.299728870391846</v>
+        <v>3.306581020355225</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2647,7 +2647,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D88">
-        <v>3.777076721191406</v>
+        <v>6.853369235992432</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2661,7 +2661,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D89">
-        <v>11.701340675354</v>
+        <v>10.42518901824951</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2675,7 +2675,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D90">
-        <v>4.546599864959717</v>
+        <v>5.169697761535645</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2689,7 +2689,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D91">
-        <v>4.940999507904053</v>
+        <v>8.045615196228027</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2703,7 +2703,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D92">
-        <v>8.249125480651855</v>
+        <v>7.457237243652344</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2717,7 +2717,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D93">
-        <v>3.53172492980957</v>
+        <v>4.588522434234619</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2731,7 +2731,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D94">
-        <v>3.930829524993896</v>
+        <v>5.081342220306396</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2745,7 +2745,7 @@
         <v>5.5</v>
       </c>
       <c r="D95">
-        <v>3.271146774291992</v>
+        <v>3.991973400115967</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2759,7 +2759,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D96">
-        <v>1.450586199760437</v>
+        <v>1.507443785667419</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2773,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="D97">
-        <v>3.076318264007568</v>
+        <v>2.905569553375244</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2787,7 +2787,7 @@
         <v>6</v>
       </c>
       <c r="D98">
-        <v>3.166173934936523</v>
+        <v>3.255120754241943</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2801,7 +2801,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D99">
-        <v>2.533913612365723</v>
+        <v>2.918204784393311</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2815,7 +2815,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D100">
-        <v>5.781317234039307</v>
+        <v>9.001580238342285</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2829,7 +2829,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D101">
-        <v>2.381643772125244</v>
+        <v>2.429855108261108</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2843,7 +2843,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D102">
-        <v>2.972874879837036</v>
+        <v>3.171376705169678</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2857,7 +2857,7 @@
         <v>21.89999961853027</v>
       </c>
       <c r="D103">
-        <v>17.93439292907715</v>
+        <v>20.40323257446289</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2871,7 +2871,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D104">
-        <v>3.389177799224854</v>
+        <v>2.918735980987549</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2885,7 +2885,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D105">
-        <v>1.376626491546631</v>
+        <v>1.257570147514343</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2899,7 +2899,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D106">
-        <v>2.478771209716797</v>
+        <v>3.500386714935303</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2913,7 +2913,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D107">
-        <v>1.258407354354858</v>
+        <v>1.198966503143311</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2927,7 +2927,7 @@
         <v>19</v>
       </c>
       <c r="D108">
-        <v>18.84432029724121</v>
+        <v>16.30335998535156</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2941,7 +2941,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D109">
-        <v>2.66284441947937</v>
+        <v>2.839863300323486</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2955,7 +2955,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D110">
-        <v>6.635612010955811</v>
+        <v>7.493610382080078</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2969,7 +2969,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D111">
-        <v>2.310516834259033</v>
+        <v>2.897154331207275</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2983,7 +2983,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D112">
-        <v>3.064037799835205</v>
+        <v>3.080514430999756</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2997,7 +2997,7 @@
         <v>1.5</v>
       </c>
       <c r="D113">
-        <v>2.123384475708008</v>
+        <v>1.486557960510254</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3011,7 +3011,7 @@
         <v>4</v>
       </c>
       <c r="D114">
-        <v>3.047111988067627</v>
+        <v>3.360743999481201</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3025,7 +3025,7 @@
         <v>11.60000038146973</v>
       </c>
       <c r="D115">
-        <v>3.638014316558838</v>
+        <v>3.149846076965332</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3039,7 +3039,7 @@
         <v>13.5</v>
       </c>
       <c r="D116">
-        <v>9.232848167419434</v>
+        <v>8.769034385681152</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3053,7 +3053,7 @@
         <v>14</v>
       </c>
       <c r="D117">
-        <v>6.813990116119385</v>
+        <v>8.21306324005127</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3067,7 +3067,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D118">
-        <v>3.911933422088623</v>
+        <v>4.949132919311523</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3081,7 +3081,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D119">
-        <v>3.615777492523193</v>
+        <v>3.382440567016602</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3095,7 +3095,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D120">
-        <v>1.975420951843262</v>
+        <v>2.556319236755371</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3109,7 +3109,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D121">
-        <v>3.353114128112793</v>
+        <v>2.746213436126709</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3123,7 +3123,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D122">
-        <v>6.432937622070312</v>
+        <v>7.261757373809814</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3137,7 +3137,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D123">
-        <v>1.620896100997925</v>
+        <v>1.288115501403809</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3151,7 +3151,7 @@
         <v>17.39999961853027</v>
       </c>
       <c r="D124">
-        <v>17.98892402648926</v>
+        <v>16.5372486114502</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3165,7 +3165,7 @@
         <v>10.60000038146973</v>
       </c>
       <c r="D125">
-        <v>11.20009517669678</v>
+        <v>11.55670356750488</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3179,7 +3179,7 @@
         <v>14.89999961853027</v>
       </c>
       <c r="D126">
-        <v>14.63783168792725</v>
+        <v>14.48031425476074</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3193,7 +3193,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D127">
-        <v>2.505230903625488</v>
+        <v>3.66107702255249</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3207,7 +3207,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D128">
-        <v>3.239712715148926</v>
+        <v>2.62014102935791</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3221,7 +3221,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D129">
-        <v>1.28082275390625</v>
+        <v>1.220086216926575</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3235,7 +3235,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D130">
-        <v>2.964457988739014</v>
+        <v>3.125944137573242</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3249,7 +3249,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D131">
-        <v>2.44036865234375</v>
+        <v>2.865547657012939</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3263,7 +3263,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D132">
-        <v>8.084502220153809</v>
+        <v>7.415462493896484</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3277,7 +3277,7 @@
         <v>19.70000076293945</v>
       </c>
       <c r="D133">
-        <v>17.06645393371582</v>
+        <v>18.13810729980469</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3291,7 +3291,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D134">
-        <v>2.461835861206055</v>
+        <v>2.955324172973633</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3305,7 +3305,7 @@
         <v>10</v>
       </c>
       <c r="D135">
-        <v>5.088842868804932</v>
+        <v>3.602197647094727</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3319,7 +3319,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D136">
-        <v>1.281263113021851</v>
+        <v>1.272237658500671</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3333,7 +3333,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D137">
-        <v>2.933346271514893</v>
+        <v>3.230386257171631</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3347,7 +3347,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D138">
-        <v>3.801225185394287</v>
+        <v>5.702933788299561</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3361,7 +3361,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D139">
-        <v>2.691483974456787</v>
+        <v>2.858250141143799</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3375,7 +3375,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D140">
-        <v>4.201251029968262</v>
+        <v>2.966059684753418</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3389,7 +3389,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D141">
-        <v>3.928374290466309</v>
+        <v>4.317673683166504</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3403,7 +3403,7 @@
         <v>21.20000076293945</v>
       </c>
       <c r="D142">
-        <v>15.56782054901123</v>
+        <v>16.74540328979492</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3417,7 +3417,7 @@
         <v>2.5</v>
       </c>
       <c r="D143">
-        <v>1.238273143768311</v>
+        <v>1.238988876342773</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3431,7 +3431,7 @@
         <v>25.89999961853027</v>
       </c>
       <c r="D144">
-        <v>11.24992084503174</v>
+        <v>7.08103609085083</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3445,7 +3445,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D145">
-        <v>4.08621883392334</v>
+        <v>5.223579883575439</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3459,7 +3459,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D146">
-        <v>3.652488231658936</v>
+        <v>3.756977558135986</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3473,7 +3473,7 @@
         <v>19.29999923706055</v>
       </c>
       <c r="D147">
-        <v>8.130721092224121</v>
+        <v>7.087227344512939</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3487,7 +3487,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D148">
-        <v>4.377449512481689</v>
+        <v>5.762842655181885</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3501,7 +3501,7 @@
         <v>10</v>
       </c>
       <c r="D149">
-        <v>8.013460159301758</v>
+        <v>6.788766384124756</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3515,7 +3515,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D150">
-        <v>8.298000335693359</v>
+        <v>7.560427188873291</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3529,7 +3529,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D151">
-        <v>3.96144437789917</v>
+        <v>3.968464374542236</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3543,7 +3543,7 @@
         <v>4.5</v>
       </c>
       <c r="D152">
-        <v>4.304999828338623</v>
+        <v>5.290978908538818</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3557,7 +3557,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D153">
-        <v>2.102010250091553</v>
+        <v>2.407454013824463</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3571,7 +3571,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D154">
-        <v>2.630650281906128</v>
+        <v>2.980486869812012</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3585,7 +3585,7 @@
         <v>9</v>
       </c>
       <c r="D155">
-        <v>2.843527317047119</v>
+        <v>2.881185054779053</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3599,7 +3599,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D156">
-        <v>3.892621517181396</v>
+        <v>4.411386966705322</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3613,7 +3613,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D157">
-        <v>8.221282005310059</v>
+        <v>6.763148307800293</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3627,7 +3627,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D158">
-        <v>17.2995777130127</v>
+        <v>11.58308219909668</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3641,7 +3641,7 @@
         <v>30.79999923706055</v>
       </c>
       <c r="D159">
-        <v>18.87460899353027</v>
+        <v>16.58481597900391</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3655,7 +3655,7 @@
         <v>11.5</v>
       </c>
       <c r="D160">
-        <v>8.027421951293945</v>
+        <v>8.337333679199219</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3669,7 +3669,7 @@
         <v>21.60000038146973</v>
       </c>
       <c r="D161">
-        <v>18.71038818359375</v>
+        <v>19.55724906921387</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3683,7 +3683,7 @@
         <v>14.60000038146973</v>
       </c>
       <c r="D162">
-        <v>10.47661876678467</v>
+        <v>12.68500804901123</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3697,7 +3697,7 @@
         <v>2.5</v>
       </c>
       <c r="D163">
-        <v>2.977992057800293</v>
+        <v>2.823328018188477</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3711,7 +3711,7 @@
         <v>2</v>
       </c>
       <c r="D164">
-        <v>3.135250091552734</v>
+        <v>2.990104198455811</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3725,7 +3725,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D165">
-        <v>2.43884801864624</v>
+        <v>2.873909950256348</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3739,7 +3739,7 @@
         <v>12.39999961853027</v>
       </c>
       <c r="D166">
-        <v>19.67230415344238</v>
+        <v>18.84816360473633</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3753,7 +3753,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D167">
-        <v>1.638049602508545</v>
+        <v>1.581369280815125</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3767,7 +3767,7 @@
         <v>2</v>
       </c>
       <c r="D168">
-        <v>3.172674655914307</v>
+        <v>3.267035961151123</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3781,7 +3781,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D169">
-        <v>7.943994998931885</v>
+        <v>9.426015853881836</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3795,7 +3795,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D170">
-        <v>1.59302282333374</v>
+        <v>1.468058586120605</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3809,7 +3809,7 @@
         <v>5</v>
       </c>
       <c r="D171">
-        <v>1.919752955436707</v>
+        <v>3.271952629089355</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3823,7 +3823,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D172">
-        <v>1.72631311416626</v>
+        <v>1.525994300842285</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3837,7 +3837,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D173">
-        <v>9.547653198242188</v>
+        <v>9.88885498046875</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3851,7 +3851,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D174">
-        <v>8.474625587463379</v>
+        <v>12.70136642456055</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3865,7 +3865,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D175">
-        <v>12.06873607635498</v>
+        <v>9.361774444580078</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3879,7 +3879,7 @@
         <v>18.5</v>
       </c>
       <c r="D176">
-        <v>18.99663925170898</v>
+        <v>18.93038749694824</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3893,7 +3893,7 @@
         <v>16.20000076293945</v>
       </c>
       <c r="D177">
-        <v>12.82939910888672</v>
+        <v>12.50883197784424</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3907,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>2.806181192398071</v>
+        <v>3.155984401702881</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3921,7 +3921,7 @@
         <v>25.29999923706055</v>
       </c>
       <c r="D179">
-        <v>19.34939765930176</v>
+        <v>13.15560150146484</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3935,7 +3935,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D180">
-        <v>10.33482646942139</v>
+        <v>10.56082534790039</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3949,7 +3949,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D181">
-        <v>4.206641674041748</v>
+        <v>9.63417911529541</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3963,7 +3963,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D182">
-        <v>8.297389030456543</v>
+        <v>7.149292469024658</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3977,7 +3977,7 @@
         <v>24</v>
       </c>
       <c r="D183">
-        <v>4.58131217956543</v>
+        <v>10.36002635955811</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3991,7 +3991,7 @@
         <v>9</v>
       </c>
       <c r="D184">
-        <v>1.960055589675903</v>
+        <v>3.097601413726807</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4005,7 +4005,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D185">
-        <v>4.361807823181152</v>
+        <v>4.131079196929932</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4019,7 +4019,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D186">
-        <v>4.889883995056152</v>
+        <v>6.201992511749268</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4033,7 +4033,7 @@
         <v>5</v>
       </c>
       <c r="D187">
-        <v>4.757660388946533</v>
+        <v>4.430539608001709</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4047,7 +4047,7 @@
         <v>10.69999980926514</v>
       </c>
       <c r="D188">
-        <v>5.280632495880127</v>
+        <v>5.776813983917236</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4061,7 +4061,7 @@
         <v>23.79999923706055</v>
       </c>
       <c r="D189">
-        <v>12.9328498840332</v>
+        <v>7.669264793395996</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4075,7 +4075,7 @@
         <v>2</v>
       </c>
       <c r="D190">
-        <v>2.763520002365112</v>
+        <v>3.052492141723633</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4089,7 +4089,7 @@
         <v>0.5</v>
       </c>
       <c r="D191">
-        <v>2.917557716369629</v>
+        <v>3.315548419952393</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4103,7 +4103,7 @@
         <v>38.79999923706055</v>
       </c>
       <c r="D192">
-        <v>23.65015983581543</v>
+        <v>24.52055168151855</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4117,7 +4117,7 @@
         <v>17.70000076293945</v>
       </c>
       <c r="D193">
-        <v>17.53470802307129</v>
+        <v>17.90544891357422</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4131,7 +4131,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D194">
-        <v>7.167591571807861</v>
+        <v>8.025568008422852</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4145,7 +4145,7 @@
         <v>18.39999961853027</v>
       </c>
       <c r="D195">
-        <v>16.69509315490723</v>
+        <v>17.82327651977539</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4159,7 +4159,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D196">
-        <v>7.309966564178467</v>
+        <v>6.945868968963623</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4173,7 +4173,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D197">
-        <v>3.255362987518311</v>
+        <v>3.347465515136719</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4187,7 +4187,7 @@
         <v>2</v>
       </c>
       <c r="D198">
-        <v>2.122738361358643</v>
+        <v>3.103000164031982</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4201,7 +4201,7 @@
         <v>13.5</v>
       </c>
       <c r="D199">
-        <v>8.145907402038574</v>
+        <v>8.037668228149414</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4215,7 +4215,7 @@
         <v>16.39999961853027</v>
       </c>
       <c r="D200">
-        <v>9.484055519104004</v>
+        <v>10.32036304473877</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4229,7 +4229,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D201">
-        <v>9.906603813171387</v>
+        <v>10.58352565765381</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4243,7 +4243,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D202">
-        <v>2.314271688461304</v>
+        <v>2.818612575531006</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4257,7 +4257,7 @@
         <v>4</v>
       </c>
       <c r="D203">
-        <v>1.720220327377319</v>
+        <v>2.788615226745605</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4271,7 +4271,7 @@
         <v>14.5</v>
       </c>
       <c r="D204">
-        <v>9.083274841308594</v>
+        <v>9.217832565307617</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4285,7 +4285,7 @@
         <v>3.5</v>
       </c>
       <c r="D205">
-        <v>2.802480220794678</v>
+        <v>2.18359637260437</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4299,7 +4299,7 @@
         <v>4.5</v>
       </c>
       <c r="D206">
-        <v>3.916037082672119</v>
+        <v>4.970291137695312</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4313,7 +4313,7 @@
         <v>5</v>
       </c>
       <c r="D207">
-        <v>8.758013725280762</v>
+        <v>11.16990566253662</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4327,7 +4327,7 @@
         <v>16.29999923706055</v>
       </c>
       <c r="D208">
-        <v>15.29560852050781</v>
+        <v>12.52521896362305</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4341,7 +4341,7 @@
         <v>19.79999923706055</v>
       </c>
       <c r="D209">
-        <v>18.62605476379395</v>
+        <v>17.70825576782227</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4355,7 +4355,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D210">
-        <v>4.339695930480957</v>
+        <v>4.245424747467041</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4369,7 +4369,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D211">
-        <v>3.1393723487854</v>
+        <v>2.924172401428223</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4383,7 +4383,7 @@
         <v>23.39999961853027</v>
       </c>
       <c r="D212">
-        <v>21.78265190124512</v>
+        <v>20.72498321533203</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4397,7 +4397,7 @@
         <v>4.5</v>
       </c>
       <c r="D213">
-        <v>2.730997562408447</v>
+        <v>3.028822898864746</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4411,7 +4411,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D214">
-        <v>1.254311919212341</v>
+        <v>1.235929608345032</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4425,7 +4425,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D215">
-        <v>8.28929615020752</v>
+        <v>7.482448101043701</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4439,7 +4439,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D216">
-        <v>3.627544403076172</v>
+        <v>5.398305416107178</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4453,7 +4453,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D217">
-        <v>1.961662769317627</v>
+        <v>2.314250469207764</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4467,7 +4467,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D218">
-        <v>3.852239608764648</v>
+        <v>3.555111408233643</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4481,7 +4481,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D219">
-        <v>5.806356906890869</v>
+        <v>4.150856494903564</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4495,7 +4495,7 @@
         <v>9</v>
       </c>
       <c r="D220">
-        <v>8.899479866027832</v>
+        <v>12.40316867828369</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4509,7 +4509,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D221">
-        <v>2.760177135467529</v>
+        <v>2.97605037689209</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4523,7 +4523,7 @@
         <v>34.70000076293945</v>
       </c>
       <c r="D222">
-        <v>14.81142616271973</v>
+        <v>12.41039276123047</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4537,7 +4537,7 @@
         <v>11.19999980926514</v>
       </c>
       <c r="D223">
-        <v>2.287193298339844</v>
+        <v>8.002785682678223</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4551,7 +4551,7 @@
         <v>17.10000038146973</v>
       </c>
       <c r="D224">
-        <v>11.43945407867432</v>
+        <v>10.82399082183838</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4565,7 +4565,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D225">
-        <v>3.234298706054688</v>
+        <v>4.488282680511475</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4579,7 +4579,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D226">
-        <v>1.951747417449951</v>
+        <v>6.217576503753662</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4593,7 +4593,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D227">
-        <v>4.576219081878662</v>
+        <v>3.921775817871094</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4607,7 +4607,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D228">
-        <v>2.10406494140625</v>
+        <v>2.903595447540283</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4621,7 +4621,7 @@
         <v>8</v>
       </c>
       <c r="D229">
-        <v>2.687849998474121</v>
+        <v>2.761605262756348</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4635,7 +4635,7 @@
         <v>1.5</v>
       </c>
       <c r="D230">
-        <v>1.741071105003357</v>
+        <v>1.485473155975342</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4649,7 +4649,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D231">
-        <v>2.742971420288086</v>
+        <v>3.122420787811279</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4663,7 +4663,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D232">
-        <v>1.422967195510864</v>
+        <v>1.206393241882324</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4677,7 +4677,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D233">
-        <v>5.332649707794189</v>
+        <v>6.128176689147949</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4691,7 +4691,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D234">
-        <v>5.445537090301514</v>
+        <v>4.881615161895752</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4705,7 +4705,7 @@
         <v>22.20000076293945</v>
       </c>
       <c r="D235">
-        <v>17.00722885131836</v>
+        <v>19.33740234375</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4719,7 +4719,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D236">
-        <v>7.801153182983398</v>
+        <v>10.16863822937012</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4733,7 +4733,7 @@
         <v>14.39999961853027</v>
       </c>
       <c r="D237">
-        <v>8.595077514648438</v>
+        <v>8.109434127807617</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4747,7 +4747,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D238">
-        <v>3.301469802856445</v>
+        <v>2.995473861694336</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4761,7 +4761,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D239">
-        <v>3.194785118103027</v>
+        <v>3.30845832824707</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4775,7 +4775,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D240">
-        <v>1.353314638137817</v>
+        <v>1.308868050575256</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4789,7 +4789,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D241">
-        <v>2.483609199523926</v>
+        <v>3.06040620803833</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4803,7 +4803,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D242">
-        <v>8.223257064819336</v>
+        <v>7.525378704071045</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4817,7 +4817,7 @@
         <v>11.19999980926514</v>
       </c>
       <c r="D243">
-        <v>7.623459339141846</v>
+        <v>4.139992237091064</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4831,7 +4831,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D244">
-        <v>1.883890390396118</v>
+        <v>1.875117301940918</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4845,7 +4845,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D245">
-        <v>4.875378131866455</v>
+        <v>4.116187572479248</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4859,7 +4859,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D246">
-        <v>8.164583206176758</v>
+        <v>7.378703117370605</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4873,7 +4873,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D247">
-        <v>1.423125505447388</v>
+        <v>1.341636896133423</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4887,7 +4887,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D248">
-        <v>5.496030330657959</v>
+        <v>6.364640712738037</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4901,7 +4901,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D249">
-        <v>3.365745067596436</v>
+        <v>4.881930351257324</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4915,7 +4915,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D250">
-        <v>2.806695222854614</v>
+        <v>2.922128677368164</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4929,7 +4929,7 @@
         <v>7.5</v>
       </c>
       <c r="D251">
-        <v>8.10911750793457</v>
+        <v>6.78566312789917</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4943,7 +4943,7 @@
         <v>20.89999961853027</v>
       </c>
       <c r="D252">
-        <v>11.09596347808838</v>
+        <v>8.57221508026123</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4957,7 +4957,7 @@
         <v>15.60000038146973</v>
       </c>
       <c r="D253">
-        <v>16.0456428527832</v>
+        <v>17.56034469604492</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4971,7 +4971,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D254">
-        <v>4.775341033935547</v>
+        <v>7.084620952606201</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4985,7 +4985,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D255">
-        <v>1.951623201370239</v>
+        <v>2.229565143585205</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4999,7 +4999,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D256">
-        <v>2.978209972381592</v>
+        <v>3.085229396820068</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -5013,7 +5013,7 @@
         <v>8.300000190734863</v>
       </c>
       <c r="D257">
-        <v>5.573183059692383</v>
+        <v>5.333444118499756</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -5027,7 +5027,7 @@
         <v>12.39999961853027</v>
       </c>
       <c r="D258">
-        <v>8.642266273498535</v>
+        <v>6.139435291290283</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -5041,7 +5041,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D259">
-        <v>7.751355648040771</v>
+        <v>6.820564746856689</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -5055,7 +5055,7 @@
         <v>10.5</v>
       </c>
       <c r="D260">
-        <v>5.79271936416626</v>
+        <v>6.048230648040771</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -5069,7 +5069,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D261">
-        <v>3.204055309295654</v>
+        <v>3.66150951385498</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -5083,7 +5083,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D262">
-        <v>4.96619176864624</v>
+        <v>4.666341781616211</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -5097,7 +5097,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D263">
-        <v>1.620210528373718</v>
+        <v>1.540223479270935</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -5111,7 +5111,7 @@
         <v>5</v>
       </c>
       <c r="D264">
-        <v>1.46835470199585</v>
+        <v>1.594113826751709</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -5125,7 +5125,7 @@
         <v>15.5</v>
       </c>
       <c r="D265">
-        <v>11.64911556243896</v>
+        <v>10.08892726898193</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -5139,7 +5139,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D266">
-        <v>1.573686361312866</v>
+        <v>1.593602657318115</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -5153,7 +5153,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D267">
-        <v>2.973350048065186</v>
+        <v>3.065056324005127</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -5167,7 +5167,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D268">
-        <v>2.846283912658691</v>
+        <v>3.008359909057617</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -5181,7 +5181,7 @@
         <v>18.89999961853027</v>
       </c>
       <c r="D269">
-        <v>7.988203525543213</v>
+        <v>13.27039623260498</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -5195,7 +5195,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D270">
-        <v>4.247598648071289</v>
+        <v>4.118459701538086</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5209,7 +5209,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D271">
-        <v>2.463121175765991</v>
+        <v>2.899468421936035</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5223,7 +5223,7 @@
         <v>18.20000076293945</v>
       </c>
       <c r="D272">
-        <v>19.97955894470215</v>
+        <v>19.65700912475586</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5237,7 +5237,7 @@
         <v>20.79999923706055</v>
       </c>
       <c r="D273">
-        <v>15.45829105377197</v>
+        <v>17.67036056518555</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5251,7 +5251,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D274">
-        <v>3.460782527923584</v>
+        <v>4.004188060760498</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5265,7 +5265,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D275">
-        <v>4.247749328613281</v>
+        <v>4.447960376739502</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5279,7 +5279,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D276">
-        <v>3.52610445022583</v>
+        <v>11.45183563232422</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5293,7 +5293,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D277">
-        <v>2.770403861999512</v>
+        <v>3.009371757507324</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5307,7 +5307,7 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>9.65797233581543</v>
+        <v>6.252330780029297</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5321,7 +5321,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D279">
-        <v>4.575935840606689</v>
+        <v>7.437028408050537</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5335,7 +5335,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D280">
-        <v>3.097231149673462</v>
+        <v>3.433290004730225</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5349,7 +5349,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D281">
-        <v>5.177789688110352</v>
+        <v>6.358493804931641</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5363,7 +5363,7 @@
         <v>15.69999980926514</v>
       </c>
       <c r="D282">
-        <v>8.238612174987793</v>
+        <v>6.998353481292725</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5377,7 +5377,7 @@
         <v>3</v>
       </c>
       <c r="D283">
-        <v>2.881455898284912</v>
+        <v>3.204010486602783</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5391,7 +5391,7 @@
         <v>0</v>
       </c>
       <c r="D284">
-        <v>1.328388929367065</v>
+        <v>1.265648007392883</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5405,7 +5405,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D285">
-        <v>3.482376098632812</v>
+        <v>4.573824405670166</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5419,7 +5419,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D286">
-        <v>8.798717498779297</v>
+        <v>9.243222236633301</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5433,7 +5433,7 @@
         <v>2</v>
       </c>
       <c r="D287">
-        <v>1.639492392539978</v>
+        <v>1.436705350875854</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5447,7 +5447,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D288">
-        <v>3.045287132263184</v>
+        <v>3.311660766601562</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5461,7 +5461,7 @@
         <v>8</v>
       </c>
       <c r="D289">
-        <v>4.489333152770996</v>
+        <v>7.240588188171387</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5475,7 +5475,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D290">
-        <v>9.44123649597168</v>
+        <v>10.02180290222168</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5489,7 +5489,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D291">
-        <v>3.768328666687012</v>
+        <v>5.668524265289307</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5503,7 +5503,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D292">
-        <v>7.678354263305664</v>
+        <v>6.527706623077393</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5517,7 +5517,7 @@
         <v>7.5</v>
       </c>
       <c r="D293">
-        <v>2.87161111831665</v>
+        <v>3.743124008178711</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5531,7 +5531,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D294">
-        <v>14.97122097015381</v>
+        <v>16.70745468139648</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5545,7 +5545,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D295">
-        <v>1.924660086631775</v>
+        <v>2.520690441131592</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5559,7 +5559,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D296">
-        <v>2.513017177581787</v>
+        <v>2.833405017852783</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5573,7 +5573,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D297">
-        <v>5.611116886138916</v>
+        <v>4.025894641876221</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5587,7 +5587,7 @@
         <v>15.60000038146973</v>
       </c>
       <c r="D298">
-        <v>15.19155979156494</v>
+        <v>13.70512771606445</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5601,7 +5601,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D299">
-        <v>4.454529762268066</v>
+        <v>5.256422519683838</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5615,7 +5615,7 @@
         <v>11.5</v>
       </c>
       <c r="D300">
-        <v>7.112098693847656</v>
+        <v>9.498324394226074</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5629,7 +5629,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D301">
-        <v>2.517519950866699</v>
+        <v>3.045741081237793</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5643,7 +5643,7 @@
         <v>12.60000038146973</v>
       </c>
       <c r="D302">
-        <v>6.915258407592773</v>
+        <v>6.506812572479248</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5657,7 +5657,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D303">
-        <v>1.196446299552917</v>
+        <v>1.201233863830566</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5671,7 +5671,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D304">
-        <v>1.23049795627594</v>
+        <v>1.262556314468384</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5685,7 +5685,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D305">
-        <v>9.459705352783203</v>
+        <v>9.485703468322754</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5699,7 +5699,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D306">
-        <v>2.757088184356689</v>
+        <v>2.642860412597656</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5713,7 +5713,7 @@
         <v>5.5</v>
       </c>
       <c r="D307">
-        <v>1.945178151130676</v>
+        <v>4.713276386260986</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5727,7 +5727,7 @@
         <v>5.5</v>
       </c>
       <c r="D308">
-        <v>2.481250286102295</v>
+        <v>3.770105361938477</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5741,7 +5741,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D309">
-        <v>3.574155330657959</v>
+        <v>3.658041954040527</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5755,7 +5755,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D310">
-        <v>4.58293342590332</v>
+        <v>5.731587409973145</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5769,7 +5769,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D311">
-        <v>5.626218318939209</v>
+        <v>7.125056266784668</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5783,7 +5783,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D312">
-        <v>2.761044025421143</v>
+        <v>2.846168994903564</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5797,7 +5797,7 @@
         <v>11.5</v>
       </c>
       <c r="D313">
-        <v>6.979567527770996</v>
+        <v>8.202031135559082</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5811,7 +5811,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D314">
-        <v>3.554151058197021</v>
+        <v>4.308462619781494</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5825,7 +5825,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D315">
-        <v>3.478254318237305</v>
+        <v>4.19745397567749</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5839,7 +5839,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D316">
-        <v>4.558874130249023</v>
+        <v>4.145005226135254</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -5853,7 +5853,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D317">
-        <v>2.827985286712646</v>
+        <v>3.004644870758057</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -5867,7 +5867,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D318">
-        <v>7.09041166305542</v>
+        <v>6.707454681396484</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -5881,7 +5881,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D319">
-        <v>1.274435639381409</v>
+        <v>1.286041140556335</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -5895,7 +5895,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D320">
-        <v>11.58411502838135</v>
+        <v>10.78105640411377</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -5909,7 +5909,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D321">
-        <v>3.576138496398926</v>
+        <v>3.25448751449585</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -5923,7 +5923,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D322">
-        <v>7.56853723526001</v>
+        <v>11.7941427230835</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -5937,7 +5937,7 @@
         <v>20.39999961853027</v>
       </c>
       <c r="D323">
-        <v>18.95424652099609</v>
+        <v>17.90428924560547</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -5951,7 +5951,7 @@
         <v>12.69999980926514</v>
       </c>
       <c r="D324">
-        <v>10.36110591888428</v>
+        <v>10.89521503448486</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -5965,7 +5965,7 @@
         <v>22.39999961853027</v>
       </c>
       <c r="D325">
-        <v>17.73164558410645</v>
+        <v>18.08156204223633</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -5979,7 +5979,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D326">
-        <v>4.794526100158691</v>
+        <v>4.867648124694824</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -5993,7 +5993,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D327">
-        <v>7.110972881317139</v>
+        <v>5.015770435333252</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -6007,7 +6007,7 @@
         <v>17.29999923706055</v>
       </c>
       <c r="D328">
-        <v>8.306820869445801</v>
+        <v>7.835518360137939</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -6021,7 +6021,7 @@
         <v>21.5</v>
       </c>
       <c r="D329">
-        <v>12.34732341766357</v>
+        <v>11.98125267028809</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -6035,7 +6035,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D330">
-        <v>1.286290168762207</v>
+        <v>1.199333310127258</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -6049,7 +6049,7 @@
         <v>1</v>
       </c>
       <c r="D331">
-        <v>7.952682495117188</v>
+        <v>7.848778247833252</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -6063,7 +6063,7 @@
         <v>16.60000038146973</v>
       </c>
       <c r="D332">
-        <v>17.16166496276855</v>
+        <v>9.704765319824219</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6077,7 +6077,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D333">
-        <v>3.575203895568848</v>
+        <v>2.699880599975586</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -6091,7 +6091,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D334">
-        <v>1.669856309890747</v>
+        <v>1.397387266159058</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -6105,7 +6105,7 @@
         <v>14.39999961853027</v>
       </c>
       <c r="D335">
-        <v>8.86680793762207</v>
+        <v>10.40291976928711</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -6119,7 +6119,7 @@
         <v>12.5</v>
       </c>
       <c r="D336">
-        <v>8.40827751159668</v>
+        <v>8.140809059143066</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -6133,7 +6133,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D337">
-        <v>6.718492031097412</v>
+        <v>7.254499912261963</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -6147,7 +6147,7 @@
         <v>10.60000038146973</v>
       </c>
       <c r="D338">
-        <v>8.141317367553711</v>
+        <v>7.28476619720459</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -6161,7 +6161,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D339">
-        <v>1.653503894805908</v>
+        <v>1.440536499023438</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -6175,7 +6175,7 @@
         <v>1</v>
       </c>
       <c r="D340">
-        <v>2.479566097259521</v>
+        <v>2.961603879928589</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -6189,7 +6189,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D341">
-        <v>1.233495831489563</v>
+        <v>1.227536916732788</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6203,7 +6203,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D342">
-        <v>1.662986159324646</v>
+        <v>1.500393390655518</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6217,7 +6217,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D343">
-        <v>3.699216365814209</v>
+        <v>4.202714920043945</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6231,7 +6231,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D344">
-        <v>8.776307106018066</v>
+        <v>10.64885997772217</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6245,7 +6245,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D345">
-        <v>12.42998504638672</v>
+        <v>17.9835319519043</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6259,7 +6259,7 @@
         <v>7</v>
       </c>
       <c r="D346">
-        <v>4.212368011474609</v>
+        <v>6.77776050567627</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6273,7 +6273,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D347">
-        <v>10.83010387420654</v>
+        <v>13.46138763427734</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6287,7 +6287,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D348">
-        <v>13.95720672607422</v>
+        <v>10.34447479248047</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6301,7 +6301,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D349">
-        <v>3.191107273101807</v>
+        <v>3.353424549102783</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6315,7 +6315,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D350">
-        <v>2.6184401512146</v>
+        <v>2.805018901824951</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6329,7 +6329,7 @@
         <v>4</v>
       </c>
       <c r="D351">
-        <v>3.390872478485107</v>
+        <v>3.243444442749023</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6343,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="D352">
-        <v>15.90169429779053</v>
+        <v>16.8239917755127</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6357,7 +6357,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D353">
-        <v>2.564337730407715</v>
+        <v>3.197582244873047</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6371,7 +6371,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D354">
-        <v>5.990724086761475</v>
+        <v>6.270203113555908</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6385,7 +6385,7 @@
         <v>14.19999980926514</v>
       </c>
       <c r="D355">
-        <v>8.08934497833252</v>
+        <v>7.689239025115967</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6399,7 +6399,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D356">
-        <v>5.863874912261963</v>
+        <v>7.252605438232422</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6413,7 +6413,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D357">
-        <v>2.829360485076904</v>
+        <v>3.064880847930908</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6427,7 +6427,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D358">
-        <v>1.790602803230286</v>
+        <v>4.917277812957764</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6441,7 +6441,7 @@
         <v>11.30000019073486</v>
       </c>
       <c r="D359">
-        <v>8.703484535217285</v>
+        <v>7.499877452850342</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6455,7 +6455,7 @@
         <v>0.5</v>
       </c>
       <c r="D360">
-        <v>1.638646125793457</v>
+        <v>1.408004760742188</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6469,7 +6469,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D361">
-        <v>6.45498514175415</v>
+        <v>5.364721298217773</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6483,7 +6483,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D362">
-        <v>3.574155330657959</v>
+        <v>3.272031784057617</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6497,7 +6497,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D363">
-        <v>3.087532043457031</v>
+        <v>3.544340133666992</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6511,7 +6511,7 @@
         <v>6.5</v>
       </c>
       <c r="D364">
-        <v>2.963314533233643</v>
+        <v>3.087078094482422</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6525,7 +6525,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D365">
-        <v>1.903658986091614</v>
+        <v>5.58338451385498</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6539,7 +6539,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D366">
-        <v>2.933239221572876</v>
+        <v>3.334922313690186</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6553,7 +6553,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D367">
-        <v>10.54996299743652</v>
+        <v>10.29248714447021</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6567,7 +6567,7 @@
         <v>40.90000152587891</v>
       </c>
       <c r="D368">
-        <v>30.8773193359375</v>
+        <v>30.37353897094727</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6581,7 +6581,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D369">
-        <v>2.930012464523315</v>
+        <v>2.830755710601807</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6595,7 +6595,7 @@
         <v>17.5</v>
       </c>
       <c r="D370">
-        <v>16.28379249572754</v>
+        <v>17.15692901611328</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6609,7 +6609,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D371">
-        <v>3.635965824127197</v>
+        <v>3.008334875106812</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6623,7 +6623,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D372">
-        <v>3.310410499572754</v>
+        <v>3.268489360809326</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6637,7 +6637,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D373">
-        <v>3.444224834442139</v>
+        <v>3.979977130889893</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6651,7 +6651,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D374">
-        <v>6.555529117584229</v>
+        <v>7.432292461395264</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6665,7 +6665,7 @@
         <v>20.39999961853027</v>
       </c>
       <c r="D375">
-        <v>2.916221618652344</v>
+        <v>7.64561128616333</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6679,7 +6679,7 @@
         <v>0.5</v>
       </c>
       <c r="D376">
-        <v>6.385912418365479</v>
+        <v>6.476565361022949</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6693,7 +6693,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D377">
-        <v>3.484869003295898</v>
+        <v>3.366721153259277</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6707,7 +6707,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D378">
-        <v>8.223789215087891</v>
+        <v>6.242113590240479</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6721,7 +6721,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D379">
-        <v>3.022582054138184</v>
+        <v>3.385733127593994</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6735,7 +6735,7 @@
         <v>7</v>
       </c>
       <c r="D380">
-        <v>8.854561805725098</v>
+        <v>16.93099594116211</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6749,7 +6749,7 @@
         <v>14.19999980926514</v>
       </c>
       <c r="D381">
-        <v>7.112965106964111</v>
+        <v>8.18025016784668</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6763,7 +6763,7 @@
         <v>1.5</v>
       </c>
       <c r="D382">
-        <v>1.247774124145508</v>
+        <v>1.207509517669678</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6777,7 +6777,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D383">
-        <v>1.44883406162262</v>
+        <v>1.314360380172729</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6791,7 +6791,7 @@
         <v>2</v>
       </c>
       <c r="D384">
-        <v>2.884768486022949</v>
+        <v>3.099377155303955</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -6805,7 +6805,7 @@
         <v>8</v>
       </c>
       <c r="D385">
-        <v>7.534852027893066</v>
+        <v>7.102299213409424</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -6819,7 +6819,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D386">
-        <v>4.126046180725098</v>
+        <v>6.345706939697266</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -6833,7 +6833,7 @@
         <v>11.5</v>
       </c>
       <c r="D387">
-        <v>8.870869636535645</v>
+        <v>9.253070831298828</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -6847,7 +6847,7 @@
         <v>8.5</v>
       </c>
       <c r="D388">
-        <v>8.866921424865723</v>
+        <v>9.417377471923828</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -6861,7 +6861,7 @@
         <v>2.5</v>
       </c>
       <c r="D389">
-        <v>2.84237813949585</v>
+        <v>3.217978000640869</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -6875,7 +6875,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D390">
-        <v>1.965711712837219</v>
+        <v>3.506157875061035</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -6889,7 +6889,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D391">
-        <v>8.647256851196289</v>
+        <v>14.18253135681152</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -6903,7 +6903,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D392">
-        <v>2.992609977722168</v>
+        <v>2.764519929885864</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -6917,7 +6917,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D393">
-        <v>1.481659531593323</v>
+        <v>1.255296230316162</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -6931,7 +6931,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D394">
-        <v>1.927140474319458</v>
+        <v>3.267090797424316</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -6945,7 +6945,7 @@
         <v>38</v>
       </c>
       <c r="D395">
-        <v>21.91628456115723</v>
+        <v>24.589111328125</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -6959,7 +6959,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D396">
-        <v>3.007440805435181</v>
+        <v>2.778278350830078</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -6973,7 +6973,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D397">
-        <v>9.297903060913086</v>
+        <v>13.13306999206543</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -6987,7 +6987,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D398">
-        <v>7.495278835296631</v>
+        <v>7.194390773773193</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -7001,7 +7001,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D399">
-        <v>7.741659641265869</v>
+        <v>7.346451282501221</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -7015,7 +7015,7 @@
         <v>10.10000038146973</v>
       </c>
       <c r="D400">
-        <v>2.822738885879517</v>
+        <v>2.80845832824707</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -7029,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="D401">
-        <v>2.056844234466553</v>
+        <v>2.133989810943604</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -7043,7 +7043,7 @@
         <v>9.5</v>
       </c>
       <c r="D402">
-        <v>3.350385665893555</v>
+        <v>5.803733825683594</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -7057,7 +7057,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D403">
-        <v>3.768999576568604</v>
+        <v>5.729645729064941</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7071,7 +7071,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D404">
-        <v>3.049356937408447</v>
+        <v>3.297086715698242</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -7085,7 +7085,7 @@
         <v>19.39999961853027</v>
       </c>
       <c r="D405">
-        <v>18.60620307922363</v>
+        <v>16.59954833984375</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7099,7 +7099,7 @@
         <v>11.5</v>
       </c>
       <c r="D406">
-        <v>9.332512855529785</v>
+        <v>10.35728073120117</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7113,7 +7113,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D407">
-        <v>1.87485671043396</v>
+        <v>1.709619522094727</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7127,7 +7127,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D408">
-        <v>2.897664308547974</v>
+        <v>2.858465194702148</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7141,7 +7141,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D409">
-        <v>4.941277503967285</v>
+        <v>5.613789558410645</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -7155,7 +7155,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D410">
-        <v>8.590945243835449</v>
+        <v>8.376765251159668</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -7169,7 +7169,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D411">
-        <v>4.084558010101318</v>
+        <v>6.200269222259521</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -7183,7 +7183,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D412">
-        <v>2.426900386810303</v>
+        <v>2.834814548492432</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -7197,7 +7197,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D413">
-        <v>2.837656497955322</v>
+        <v>2.953041553497314</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7211,7 +7211,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D414">
-        <v>3.999162673950195</v>
+        <v>4.330957412719727</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7225,7 +7225,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D415">
-        <v>2.800966739654541</v>
+        <v>3.030320644378662</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7239,7 +7239,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D416">
-        <v>3.647731781005859</v>
+        <v>3.924686908721924</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7253,7 +7253,7 @@
         <v>14.39999961853027</v>
       </c>
       <c r="D417">
-        <v>5.891139984130859</v>
+        <v>7.475640773773193</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7267,7 +7267,7 @@
         <v>20.70000076293945</v>
       </c>
       <c r="D418">
-        <v>18.2641429901123</v>
+        <v>17.53672409057617</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7281,7 +7281,7 @@
         <v>12.30000019073486</v>
       </c>
       <c r="D419">
-        <v>4.792625427246094</v>
+        <v>3.881264209747314</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7295,7 +7295,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D420">
-        <v>2.842918395996094</v>
+        <v>3.509852886199951</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7309,7 +7309,7 @@
         <v>9.600000381469727</v>
       </c>
       <c r="D421">
-        <v>1.79832124710083</v>
+        <v>2.660511016845703</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7323,7 +7323,7 @@
         <v>14.39999961853027</v>
       </c>
       <c r="D422">
-        <v>8.901413917541504</v>
+        <v>9.181784629821777</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7337,7 +7337,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D423">
-        <v>3.069723606109619</v>
+        <v>3.016575574874878</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7351,7 +7351,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D424">
-        <v>1.237711787223816</v>
+        <v>1.219016075134277</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7365,7 +7365,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D425">
-        <v>1.346215605735779</v>
+        <v>1.2287677526474</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7379,7 +7379,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D426">
-        <v>1.348887085914612</v>
+        <v>1.227331399917603</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7393,7 +7393,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D427">
-        <v>1.864237308502197</v>
+        <v>2.171257495880127</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7407,7 +7407,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D428">
-        <v>6.087110996246338</v>
+        <v>6.248095035552979</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7421,7 +7421,7 @@
         <v>3.5</v>
       </c>
       <c r="D429">
-        <v>5.138783931732178</v>
+        <v>7.820159435272217</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7435,7 +7435,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D430">
-        <v>1.675833225250244</v>
+        <v>1.452842712402344</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7449,7 +7449,7 @@
         <v>29.60000038146973</v>
       </c>
       <c r="D431">
-        <v>22.46104431152344</v>
+        <v>24.30465316772461</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7463,7 +7463,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D432">
-        <v>1.856305360794067</v>
+        <v>4.067807197570801</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7477,7 +7477,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D433">
-        <v>2.81844162940979</v>
+        <v>3.748879909515381</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7491,7 +7491,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D434">
-        <v>2.765213251113892</v>
+        <v>3.214118480682373</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7505,7 +7505,7 @@
         <v>19.5</v>
       </c>
       <c r="D435">
-        <v>18.63356399536133</v>
+        <v>19.04050064086914</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7519,7 +7519,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D436">
-        <v>4.434282779693604</v>
+        <v>6.984145164489746</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7533,7 +7533,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D437">
-        <v>3.478269100189209</v>
+        <v>3.167603492736816</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7547,7 +7547,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D438">
-        <v>3.020040035247803</v>
+        <v>3.496846675872803</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7561,7 +7561,7 @@
         <v>18.5</v>
       </c>
       <c r="D439">
-        <v>7.077582359313965</v>
+        <v>6.401641368865967</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7575,7 +7575,7 @@
         <v>18</v>
       </c>
       <c r="D440">
-        <v>14.6458625793457</v>
+        <v>19.22163200378418</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7589,7 +7589,7 @@
         <v>8.5</v>
       </c>
       <c r="D441">
-        <v>6.376885890960693</v>
+        <v>6.529926776885986</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7603,7 +7603,7 @@
         <v>9</v>
       </c>
       <c r="D442">
-        <v>8.17817211151123</v>
+        <v>10.38941669464111</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7617,7 +7617,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D443">
-        <v>1.200909495353699</v>
+        <v>1.224292278289795</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7631,7 +7631,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D444">
-        <v>2.773623943328857</v>
+        <v>4.052007675170898</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7645,7 +7645,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D445">
-        <v>2.839675664901733</v>
+        <v>2.82830286026001</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7659,7 +7659,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D446">
-        <v>1.280080318450928</v>
+        <v>1.244224190711975</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7673,7 +7673,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D447">
-        <v>2.607998847961426</v>
+        <v>2.937546491622925</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7687,7 +7687,7 @@
         <v>14.69999980926514</v>
       </c>
       <c r="D448">
-        <v>9.283164024353027</v>
+        <v>9.922811508178711</v>
       </c>
     </row>
     <row r="449" spans="1:4">
@@ -7701,7 +7701,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D449">
-        <v>7.229401111602783</v>
+        <v>8.156998634338379</v>
       </c>
     </row>
     <row r="450" spans="1:4">
@@ -7715,7 +7715,7 @@
         <v>16.60000038146973</v>
       </c>
       <c r="D450">
-        <v>15.9382209777832</v>
+        <v>18.4718132019043</v>
       </c>
     </row>
     <row r="451" spans="1:4">
@@ -7729,7 +7729,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D451">
-        <v>5.516458034515381</v>
+        <v>7.023260116577148</v>
       </c>
     </row>
     <row r="452" spans="1:4">
@@ -7743,7 +7743,7 @@
         <v>9</v>
       </c>
       <c r="D452">
-        <v>7.868826389312744</v>
+        <v>4.286593914031982</v>
       </c>
     </row>
     <row r="453" spans="1:4">
@@ -7757,7 +7757,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D453">
-        <v>3.559817790985107</v>
+        <v>3.973792552947998</v>
       </c>
     </row>
     <row r="454" spans="1:4">
@@ -7771,7 +7771,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D454">
-        <v>3.914618492126465</v>
+        <v>4.820675849914551</v>
       </c>
     </row>
     <row r="455" spans="1:4">
@@ -7785,7 +7785,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D455">
-        <v>4.132903575897217</v>
+        <v>4.469613075256348</v>
       </c>
     </row>
     <row r="456" spans="1:4">
@@ -7799,7 +7799,7 @@
         <v>39.90000152587891</v>
       </c>
       <c r="D456">
-        <v>29.37448883056641</v>
+        <v>23.45015335083008</v>
       </c>
     </row>
     <row r="457" spans="1:4">
@@ -7813,7 +7813,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D457">
-        <v>2.971822738647461</v>
+        <v>3.132901668548584</v>
       </c>
     </row>
     <row r="458" spans="1:4">
@@ -7827,7 +7827,7 @@
         <v>23.70000076293945</v>
       </c>
       <c r="D458">
-        <v>23.63010597229004</v>
+        <v>19.95515251159668</v>
       </c>
     </row>
     <row r="459" spans="1:4">
@@ -7841,7 +7841,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D459">
-        <v>1.574498295783997</v>
+        <v>1.355130910873413</v>
       </c>
     </row>
     <row r="460" spans="1:4">
@@ -7855,7 +7855,7 @@
         <v>10.5</v>
       </c>
       <c r="D460">
-        <v>2.76110577583313</v>
+        <v>3.178624153137207</v>
       </c>
     </row>
     <row r="461" spans="1:4">
@@ -7869,7 +7869,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D461">
-        <v>4.801933765411377</v>
+        <v>4.091038227081299</v>
       </c>
     </row>
     <row r="462" spans="1:4">
@@ -7883,7 +7883,7 @@
         <v>18.79999923706055</v>
       </c>
       <c r="D462">
-        <v>16.9518928527832</v>
+        <v>17.9241886138916</v>
       </c>
     </row>
     <row r="463" spans="1:4">
@@ -7897,7 +7897,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D463">
-        <v>5.225935459136963</v>
+        <v>7.36527681350708</v>
       </c>
     </row>
     <row r="464" spans="1:4">
@@ -7911,7 +7911,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D464">
-        <v>1.754990100860596</v>
+        <v>1.573340535163879</v>
       </c>
     </row>
     <row r="465" spans="1:4">
@@ -7925,7 +7925,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D465">
-        <v>1.27925705909729</v>
+        <v>1.263878345489502</v>
       </c>
     </row>
     <row r="466" spans="1:4">
@@ -7939,7 +7939,7 @@
         <v>2</v>
       </c>
       <c r="D466">
-        <v>2.993101596832275</v>
+        <v>3.489320278167725</v>
       </c>
     </row>
     <row r="467" spans="1:4">
@@ -7953,7 +7953,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D467">
-        <v>1.495919466018677</v>
+        <v>1.371096611022949</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -7967,7 +7967,7 @@
         <v>11.60000038146973</v>
       </c>
       <c r="D468">
-        <v>1.672063708305359</v>
+        <v>4.805776119232178</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -7981,7 +7981,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D469">
-        <v>3.391044616699219</v>
+        <v>2.956866264343262</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -7995,7 +7995,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D470">
-        <v>2.769500255584717</v>
+        <v>2.740050792694092</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -8009,7 +8009,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D471">
-        <v>8.363158226013184</v>
+        <v>7.538286685943604</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -8023,7 +8023,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D472">
-        <v>3.226663112640381</v>
+        <v>3.117933750152588</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -8037,7 +8037,7 @@
         <v>1.5</v>
       </c>
       <c r="D473">
-        <v>3.259160995483398</v>
+        <v>2.933402538299561</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -8051,7 +8051,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D474">
-        <v>1.191647291183472</v>
+        <v>1.21579909324646</v>
       </c>
     </row>
     <row r="475" spans="1:4">
@@ -8065,7 +8065,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D475">
-        <v>4.498824119567871</v>
+        <v>6.941586971282959</v>
       </c>
     </row>
     <row r="476" spans="1:4">
@@ -8079,7 +8079,7 @@
         <v>1</v>
       </c>
       <c r="D476">
-        <v>1.179256081581116</v>
+        <v>1.237543106079102</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -8093,7 +8093,7 @@
         <v>18.89999961853027</v>
       </c>
       <c r="D477">
-        <v>15.63423442840576</v>
+        <v>16.61987495422363</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -8107,7 +8107,7 @@
         <v>1.5</v>
       </c>
       <c r="D478">
-        <v>5.485114574432373</v>
+        <v>6.566105842590332</v>
       </c>
     </row>
     <row r="479" spans="1:4">
@@ -8121,7 +8121,7 @@
         <v>6.5</v>
       </c>
       <c r="D479">
-        <v>4.254317283630371</v>
+        <v>5.675085067749023</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -8135,7 +8135,7 @@
         <v>2</v>
       </c>
       <c r="D480">
-        <v>3.367504596710205</v>
+        <v>3.210075378417969</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -8149,7 +8149,7 @@
         <v>0.5</v>
       </c>
       <c r="D481">
-        <v>1.38601016998291</v>
+        <v>1.3292316198349</v>
       </c>
     </row>
     <row r="482" spans="1:4">
@@ -8163,7 +8163,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D482">
-        <v>2.925771713256836</v>
+        <v>2.854221343994141</v>
       </c>
     </row>
     <row r="483" spans="1:4">
@@ -8177,7 +8177,7 @@
         <v>24.79999923706055</v>
       </c>
       <c r="D483">
-        <v>13.40892696380615</v>
+        <v>14.41292762756348</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -8191,7 +8191,7 @@
         <v>5.5</v>
       </c>
       <c r="D484">
-        <v>2.259785175323486</v>
+        <v>2.78612232208252</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -8205,7 +8205,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D485">
-        <v>1.793317437171936</v>
+        <v>7.288390636444092</v>
       </c>
     </row>
     <row r="486" spans="1:4">
@@ -8219,7 +8219,7 @@
         <v>5.5</v>
       </c>
       <c r="D486">
-        <v>2.117655515670776</v>
+        <v>2.913708209991455</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -8233,7 +8233,7 @@
         <v>15</v>
       </c>
       <c r="D487">
-        <v>10.04232406616211</v>
+        <v>10.07954597473145</v>
       </c>
     </row>
     <row r="488" spans="1:4">
@@ -8247,7 +8247,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D488">
-        <v>3.776412487030029</v>
+        <v>4.583517551422119</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -8261,7 +8261,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D489">
-        <v>2.22722864151001</v>
+        <v>2.532788753509521</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -8275,7 +8275,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D490">
-        <v>2.762568473815918</v>
+        <v>3.167548179626465</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -8289,7 +8289,7 @@
         <v>10.39999961853027</v>
       </c>
       <c r="D491">
-        <v>4.347855567932129</v>
+        <v>5.040858745574951</v>
       </c>
     </row>
     <row r="492" spans="1:4">
@@ -8303,7 +8303,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D492">
-        <v>8.260897636413574</v>
+        <v>7.157012939453125</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -8317,7 +8317,7 @@
         <v>12.19999980926514</v>
       </c>
       <c r="D493">
-        <v>7.173704147338867</v>
+        <v>6.464754104614258</v>
       </c>
     </row>
     <row r="494" spans="1:4">
@@ -8331,7 +8331,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D494">
-        <v>1.837513446807861</v>
+        <v>2.755248546600342</v>
       </c>
     </row>
     <row r="495" spans="1:4">
@@ -8345,7 +8345,7 @@
         <v>16.39999961853027</v>
       </c>
       <c r="D495">
-        <v>7.805479526519775</v>
+        <v>6.540083408355713</v>
       </c>
     </row>
     <row r="496" spans="1:4">
@@ -8359,7 +8359,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D496">
-        <v>2.898857116699219</v>
+        <v>3.179287433624268</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -8373,7 +8373,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D497">
-        <v>7.176080226898193</v>
+        <v>9.00485897064209</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -8387,7 +8387,7 @@
         <v>1.5</v>
       </c>
       <c r="D498">
-        <v>3.305373191833496</v>
+        <v>3.028214931488037</v>
       </c>
     </row>
     <row r="499" spans="1:4">
@@ -8401,7 +8401,7 @@
         <v>12.60000038146973</v>
       </c>
       <c r="D499">
-        <v>8.247800827026367</v>
+        <v>8.528671264648438</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -8415,7 +8415,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D500">
-        <v>2.913029670715332</v>
+        <v>3.131587982177734</v>
       </c>
     </row>
     <row r="501" spans="1:4">
@@ -8429,7 +8429,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D501">
-        <v>1.639599919319153</v>
+        <v>1.454462289810181</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -8443,7 +8443,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D502">
-        <v>5.040016174316406</v>
+        <v>5.15108585357666</v>
       </c>
     </row>
     <row r="503" spans="1:4">
@@ -8457,7 +8457,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D503">
-        <v>2.567261695861816</v>
+        <v>2.105135440826416</v>
       </c>
     </row>
     <row r="504" spans="1:4">
@@ -8471,7 +8471,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D504">
-        <v>2.026747226715088</v>
+        <v>3.156664848327637</v>
       </c>
     </row>
     <row r="505" spans="1:4">
@@ -8485,7 +8485,7 @@
         <v>13.60000038146973</v>
       </c>
       <c r="D505">
-        <v>8.76368522644043</v>
+        <v>9.231353759765625</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -8499,7 +8499,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D506">
-        <v>16.3284912109375</v>
+        <v>12.33525848388672</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -8513,7 +8513,7 @@
         <v>12.60000038146973</v>
       </c>
       <c r="D507">
-        <v>6.411537647247314</v>
+        <v>6.653613090515137</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -8527,7 +8527,7 @@
         <v>10.60000038146973</v>
       </c>
       <c r="D508">
-        <v>9.845308303833008</v>
+        <v>10.46285820007324</v>
       </c>
     </row>
     <row r="509" spans="1:4">
@@ -8541,7 +8541,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D509">
-        <v>4.56967306137085</v>
+        <v>5.962109088897705</v>
       </c>
     </row>
     <row r="510" spans="1:4">
@@ -8555,7 +8555,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D510">
-        <v>5.504629135131836</v>
+        <v>6.68831729888916</v>
       </c>
     </row>
     <row r="511" spans="1:4">
@@ -8569,7 +8569,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D511">
-        <v>3.018556594848633</v>
+        <v>1.449952006340027</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -8583,7 +8583,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D512">
-        <v>1.29961884021759</v>
+        <v>1.271130084991455</v>
       </c>
     </row>
     <row r="513" spans="1:4">
@@ -8597,7 +8597,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D513">
-        <v>1.956769943237305</v>
+        <v>2.692448616027832</v>
       </c>
     </row>
     <row r="514" spans="1:4">
@@ -8611,7 +8611,7 @@
         <v>1</v>
       </c>
       <c r="D514">
-        <v>3.448119163513184</v>
+        <v>4.498095512390137</v>
       </c>
     </row>
     <row r="515" spans="1:4">
@@ -8625,7 +8625,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D515">
-        <v>3.563741207122803</v>
+        <v>3.439321517944336</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -8639,7 +8639,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D516">
-        <v>1.308238744735718</v>
+        <v>1.372607707977295</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -8653,7 +8653,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D517">
-        <v>5.662130832672119</v>
+        <v>5.164793014526367</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -8667,7 +8667,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D518">
-        <v>3.373220920562744</v>
+        <v>3.977334499359131</v>
       </c>
     </row>
     <row r="519" spans="1:4">
@@ -8681,7 +8681,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D519">
-        <v>5.622031688690186</v>
+        <v>5.866146087646484</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -8695,7 +8695,7 @@
         <v>8</v>
       </c>
       <c r="D520">
-        <v>3.099338054656982</v>
+        <v>3.507559776306152</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -8709,7 +8709,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D521">
-        <v>3.634475231170654</v>
+        <v>3.861961364746094</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -8723,7 +8723,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D522">
-        <v>7.543833255767822</v>
+        <v>6.224560260772705</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -8737,7 +8737,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D523">
-        <v>7.013876914978027</v>
+        <v>6.135875225067139</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -8751,7 +8751,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D524">
-        <v>1.577392816543579</v>
+        <v>1.427972674369812</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -8765,7 +8765,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D525">
-        <v>4.008049488067627</v>
+        <v>5.447405815124512</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -8779,7 +8779,7 @@
         <v>9.199999809265137</v>
       </c>
       <c r="D526">
-        <v>3.022385120391846</v>
+        <v>3.409603118896484</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -8793,7 +8793,7 @@
         <v>14</v>
       </c>
       <c r="D527">
-        <v>15.80960369110107</v>
+        <v>18.13263893127441</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -8807,7 +8807,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D528">
-        <v>8.654671669006348</v>
+        <v>10.73672103881836</v>
       </c>
     </row>
     <row r="529" spans="1:4">
@@ -8821,7 +8821,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D529">
-        <v>4.257111072540283</v>
+        <v>4.474915027618408</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -8835,7 +8835,7 @@
         <v>3.5</v>
       </c>
       <c r="D530">
-        <v>2.708441734313965</v>
+        <v>3.062016487121582</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -8849,7 +8849,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D531">
-        <v>2.327054977416992</v>
+        <v>2.695846557617188</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -8863,7 +8863,7 @@
         <v>12.39999961853027</v>
       </c>
       <c r="D532">
-        <v>8.750873565673828</v>
+        <v>11.24527835845947</v>
       </c>
     </row>
     <row r="533" spans="1:4">
@@ -8877,7 +8877,7 @@
         <v>10.10000038146973</v>
       </c>
       <c r="D533">
-        <v>8.205053329467773</v>
+        <v>7.232641696929932</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -8891,7 +8891,7 @@
         <v>26</v>
       </c>
       <c r="D534">
-        <v>16.50514030456543</v>
+        <v>20.07599639892578</v>
       </c>
     </row>
     <row r="535" spans="1:4">
@@ -8905,7 +8905,7 @@
         <v>19.79999923706055</v>
       </c>
       <c r="D535">
-        <v>19.19580459594727</v>
+        <v>20.39803504943848</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -8919,7 +8919,7 @@
         <v>2</v>
       </c>
       <c r="D536">
-        <v>1.864025235176086</v>
+        <v>1.871423244476318</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -8933,7 +8933,7 @@
         <v>2.5</v>
       </c>
       <c r="D537">
-        <v>1.588019847869873</v>
+        <v>3.898458957672119</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -8947,7 +8947,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D538">
-        <v>2.768215179443359</v>
+        <v>3.108388900756836</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -8961,7 +8961,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D539">
-        <v>6.686133861541748</v>
+        <v>6.3711838722229</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -8975,7 +8975,7 @@
         <v>13</v>
       </c>
       <c r="D540">
-        <v>5.761947631835938</v>
+        <v>9.239412307739258</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -8989,7 +8989,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D541">
-        <v>5.733450412750244</v>
+        <v>2.263956069946289</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -9003,7 +9003,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D542">
-        <v>4.000206470489502</v>
+        <v>4.125843048095703</v>
       </c>
     </row>
     <row r="543" spans="1:4">
@@ -9017,7 +9017,7 @@
         <v>15.19999980926514</v>
       </c>
       <c r="D543">
-        <v>12.60664081573486</v>
+        <v>12.28943252563477</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -9031,7 +9031,7 @@
         <v>7</v>
       </c>
       <c r="D544">
-        <v>13.32298183441162</v>
+        <v>16.60132026672363</v>
       </c>
     </row>
     <row r="545" spans="1:4">
@@ -9045,7 +9045,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D545">
-        <v>1.241646289825439</v>
+        <v>1.232916831970215</v>
       </c>
     </row>
     <row r="546" spans="1:4">
@@ -9059,7 +9059,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D546">
-        <v>4.155170440673828</v>
+        <v>3.918001174926758</v>
       </c>
     </row>
     <row r="547" spans="1:4">
@@ -9073,7 +9073,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D547">
-        <v>2.306784629821777</v>
+        <v>2.712740421295166</v>
       </c>
     </row>
     <row r="548" spans="1:4">
@@ -9087,7 +9087,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D548">
-        <v>2.188649654388428</v>
+        <v>2.570226669311523</v>
       </c>
     </row>
     <row r="549" spans="1:4">
@@ -9101,7 +9101,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D549">
-        <v>2.866922855377197</v>
+        <v>3.187828063964844</v>
       </c>
     </row>
     <row r="550" spans="1:4">
@@ -9115,7 +9115,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D550">
-        <v>5.643044948577881</v>
+        <v>6.548703670501709</v>
       </c>
     </row>
     <row r="551" spans="1:4">
@@ -9129,7 +9129,7 @@
         <v>17.20000076293945</v>
       </c>
       <c r="D551">
-        <v>16.62508964538574</v>
+        <v>16.76555442810059</v>
       </c>
     </row>
     <row r="552" spans="1:4">
@@ -9143,7 +9143,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D552">
-        <v>4.129051208496094</v>
+        <v>4.80233907699585</v>
       </c>
     </row>
   </sheetData>
